--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487825_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487825_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. YARNOZ LUMBRERAS</t>
+          <t>P. FERNANDEZ CHOCARRO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3056</v>
+        <v>0.2295</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.8364</v>
+        <v>-0.528</v>
       </c>
       <c r="F2" t="n">
-        <v>2.142</v>
+        <v>0.7574</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.3545</v>
+        <v>-2.1123</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2474</v>
+        <v>-1.0338</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.6018</v>
+        <v>-1.0785</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.4072</v>
+        <v>-1.1159</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4111</v>
+        <v>0.3218</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.8183</v>
+        <v>-1.4377</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0527</v>
+        <v>-0.9964</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1637</v>
+        <v>-1.3556</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2165</v>
+        <v>0.3592</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2081</v>
+        <v>1.4568</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2893</v>
+        <v>1.4568</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2844</v>
+        <v>-0.7602</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8383</v>
+        <v>-0.5795</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5538</v>
+        <v>-0.1807</v>
       </c>
       <c r="V2" t="n">
+        <v>1.6452</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.1675</v>
       </c>
-      <c r="W2" t="n">
-        <v>0.8137</v>
-      </c>
       <c r="X2" t="n">
-        <v>0.3538</v>
+        <v>0.4776</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1337</v>
+        <v>0.0162</v>
       </c>
       <c r="E3" t="n">
         <v>0.0776</v>
       </c>
       <c r="F3" t="n">
-        <v>0.056</v>
+        <v>-0.0614</v>
       </c>
       <c r="G3" t="n">
         <v>-0.1919</v>
@@ -688,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3256</v>
+        <v>0.2081</v>
       </c>
       <c r="T3" t="n">
         <v>0.0776</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2479</v>
+        <v>0.1305</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0653</v>
       </c>
       <c r="E4" t="n">
         <v>0.0776</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1723</v>
+        <v>-0.1429</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1919</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.1266</v>
       </c>
       <c r="T4" t="n">
         <v>0.0776</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0196</v>
+        <v>0.0489</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ CHOCARRO</t>
+          <t>P. YARNOZ LUMBRERAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3041</v>
+        <v>-0.1481</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9147</v>
+        <v>-2.3488</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6106</v>
+        <v>2.2007</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.1123</v>
+        <v>-1.3545</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0338</v>
+        <v>0.2474</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0785</v>
+        <v>-1.6018</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.1159</v>
+        <v>-1.4072</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3218</v>
+        <v>1.4111</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.4377</v>
+        <v>-2.8183</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9964</v>
+        <v>0.0527</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3556</v>
+        <v>-1.1637</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3592</v>
+        <v>1.2165</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4568</v>
+        <v>0.2081</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4568</v>
+        <v>2.2893</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2937</v>
+        <v>-0.1693</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9663</v>
+        <v>0.3258</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3275</v>
+        <v>-0.4951</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6452</v>
+        <v>1.1675</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1675</v>
+        <v>0.8137</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4776</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1191</v>
+        <v>-0.8945</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9238</v>
+        <v>-0.8166</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1954</v>
+        <v>-0.0779</v>
       </c>
       <c r="G6" t="n">
         <v>-1.157</v>
@@ -922,13 +922,13 @@
         <v>0.2081</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1703</v>
+        <v>0.0543</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2486</v>
+        <v>-0.1414</v>
       </c>
       <c r="U6" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.1957</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2103</v>
+        <v>-1.4163</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1865</v>
+        <v>-1.6273</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0238</v>
+        <v>0.2111</v>
       </c>
       <c r="G7" t="n">
         <v>-2.5283</v>
@@ -1000,13 +1000,13 @@
         <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3688</v>
+        <v>-0.5748</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.162</v>
+        <v>-0.6029</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2068</v>
+        <v>0.0281</v>
       </c>
       <c r="V7" t="n">
         <v>0.23</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ALFAMA AMADO</t>
+          <t>J. LACUNZA ABECIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7858</v>
+        <v>-2.7566</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6984</v>
+        <v>-5.1172</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0874</v>
+        <v>2.3606</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3841</v>
+        <v>-4.6153</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.7483</v>
+        <v>-1.6632</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3642</v>
+        <v>-2.9522</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1471</v>
+        <v>-4.5377</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.107</v>
+        <v>-1.7977</v>
       </c>
       <c r="L8" t="n">
-        <v>1.254</v>
+        <v>-2.7399</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5311</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6414</v>
+        <v>0.1346</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1102</v>
+        <v>-0.2123</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.6649</v>
+        <v>1.6649</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4307</v>
+        <v>-0.16</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0464</v>
+        <v>-0.5795</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3844</v>
+        <v>0.4195</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1675</v>
+        <v>0.3538</v>
       </c>
       <c r="W8" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3975</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. LACUNZA ABECIA</t>
+          <t>A. CALVO TORRES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.326</v>
+        <v>-3.4162</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.5692</v>
+        <v>-3.0869</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2432</v>
+        <v>-0.3292</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.6153</v>
+        <v>-0.9194</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6632</v>
+        <v>0.2881</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.9522</v>
+        <v>-1.2075</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.5377</v>
+        <v>0.0319</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.7977</v>
+        <v>0.921</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.7399</v>
+        <v>-0.8891</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.9513</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1346</v>
+        <v>-0.6329</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2123</v>
+        <v>-0.3184</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6649</v>
+        <v>-2.0812</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7294</v>
+        <v>-0.1856</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0315</v>
+        <v>0.0029</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3021</v>
+        <v>-0.1885</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3538</v>
+        <v>-0.23</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3538</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. DJERY</t>
+          <t>A. ALFAMA AMADO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2467</v>
+        <v>-4.4278</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5587</v>
+        <v>-2.8118</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.688</v>
+        <v>-1.6159</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8927</v>
+        <v>-1.3841</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.1875</v>
+        <v>-2.7483</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2947</v>
+        <v>1.3642</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2352</v>
+        <v>0.1471</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3136</v>
+        <v>-1.107</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0784</v>
+        <v>1.254</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6575</v>
+        <v>-1.5311</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8738</v>
+        <v>-1.6414</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2164</v>
+        <v>0.1102</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6244</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0812</v>
+        <v>-3.1218</v>
       </c>
       <c r="R10" t="n">
         <v>1.4568</v>
       </c>
       <c r="S10" t="n">
-        <v>1.543</v>
+        <v>-0.2112</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5276999999999999</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0152</v>
+        <v>-0.1441</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.2726</v>
+        <v>-1.1675</v>
       </c>
       <c r="W10" t="n">
         <v>0.23</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.5026</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. CALVO TORRES</t>
+          <t>J. DJERY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3951</v>
+        <v>-5.1614</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8604</v>
+        <v>-2.8569</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5347</v>
+        <v>-2.3046</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9194</v>
+        <v>-1.8927</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2881</v>
+        <v>-2.1875</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2075</v>
+        <v>0.2947</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0319</v>
+        <v>-1.2352</v>
       </c>
       <c r="K11" t="n">
-        <v>0.921</v>
+        <v>-1.3136</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.8891</v>
+        <v>0.0784</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9513</v>
+        <v>-0.6575</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6329</v>
+        <v>-0.8738</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3184</v>
+        <v>0.2164</v>
       </c>
       <c r="P11" t="n">
+        <v>-0.6244</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-2.0812</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-3.1218</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.0406</v>
+        <v>1.4568</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1646</v>
+        <v>0.6283</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7705</v>
+        <v>0.2296</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.394</v>
+        <v>0.3987</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.23</v>
+        <v>-3.2726</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.23</v>
+        <v>-3.5026</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3109</v>
+        <v>-5.2647</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1691</v>
+        <v>-4.211</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1417</v>
+        <v>-1.0537</v>
       </c>
       <c r="G12" t="n">
         <v>-1.862</v>
@@ -1390,13 +1390,13 @@
         <v>1.4568</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4104</v>
+        <v>-0.3642</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3849</v>
+        <v>0.3429</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7952</v>
+        <v>-0.7071</v>
       </c>
       <c r="V12" t="n">
         <v>0.7076</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.3751</v>
+        <v>-7.4446</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.4814</v>
+        <v>-5.8151</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8937</v>
+        <v>-1.6294</v>
       </c>
       <c r="G13" t="n">
         <v>-1.6311</v>
@@ -1468,13 +1468,13 @@
         <v>2.0812</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8679</v>
+        <v>-0.9374</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2925</v>
+        <v>-0.6262</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5754</v>
+        <v>-0.3111</v>
       </c>
       <c r="V13" t="n">
         <v>-2.795</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-31.7285</v>
+        <v>-30.7498</v>
       </c>
       <c r="E14" t="n">
-        <v>-30.0434</v>
+        <v>-29.0644</v>
       </c>
       <c r="F14" t="n">
         <v>-1.6852</v>
@@ -1516,7 +1516,7 @@
         <v>-11.9823</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.858200000000001</v>
+        <v>-7.8582</v>
       </c>
       <c r="J14" t="n">
         <v>-11.5918</v>
@@ -1546,13 +1546,13 @@
         <v>14.5681</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.3242</v>
+        <v>-2.3454</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.5189</v>
+        <v>-1.5402</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8051999999999998</v>
+        <v>-0.8051999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-3.361</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.6414</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>4.047</v>
+        <v>4.3684</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5944</v>
+        <v>4.0015</v>
       </c>
       <c r="G15" t="n">
         <v>6.3157</v>
@@ -1624,13 +1624,13 @@
         <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0333</v>
+        <v>0.7619</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0033</v>
+        <v>0.3182</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0366</v>
+        <v>0.4437</v>
       </c>
       <c r="V15" t="n">
         <v>0.4599</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.1251</v>
+        <v>5.9656</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7258</v>
+        <v>2.5115</v>
       </c>
       <c r="F16" t="n">
-        <v>3.3993</v>
+        <v>3.4541</v>
       </c>
       <c r="G16" t="n">
         <v>4.7736</v>
@@ -1702,13 +1702,13 @@
         <v>1.6649</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1652</v>
+        <v>1.0057</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6458</v>
+        <v>0.4315</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5194</v>
+        <v>0.5742</v>
       </c>
       <c r="V16" t="n">
         <v>-0.23</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.3497</v>
+        <v>5.448</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7365</v>
+        <v>3.6294</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6131</v>
+        <v>1.8187</v>
       </c>
       <c r="G17" t="n">
         <v>3.641</v>
@@ -1780,13 +1780,13 @@
         <v>2.4974</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4599</v>
+        <v>0.5583</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5806</v>
+        <v>0.4734</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1207</v>
+        <v>0.0849</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.2328</v>
+        <v>4.8678</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1729</v>
+        <v>-0.3872</v>
       </c>
       <c r="F18" t="n">
-        <v>5.4058</v>
+        <v>5.2551</v>
       </c>
       <c r="G18" t="n">
         <v>3.0524</v>
@@ -1858,13 +1858,13 @@
         <v>2.4974</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6154</v>
+        <v>1.2504</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5806</v>
+        <v>0.3663</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0348</v>
+        <v>0.8841</v>
       </c>
       <c r="V18" t="n">
         <v>1.3975</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.9599</v>
+        <v>4.1028</v>
       </c>
       <c r="E19" t="n">
         <v>1.8268</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1331</v>
+        <v>2.276</v>
       </c>
       <c r="G19" t="n">
         <v>0.1521</v>
@@ -1936,13 +1936,13 @@
         <v>2.4974</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1429</v>
+        <v>0.2857</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0033</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1462</v>
+        <v>0.2891</v>
       </c>
       <c r="V19" t="n">
         <v>1.1675</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.2417</v>
+        <v>3.2735</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1698</v>
+        <v>0.0626</v>
       </c>
       <c r="F20" t="n">
-        <v>3.0719</v>
+        <v>3.2108</v>
       </c>
       <c r="G20" t="n">
         <v>1.4099</v>
@@ -2014,13 +2014,13 @@
         <v>1.4568</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4769</v>
+        <v>0.5087</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0619</v>
+        <v>-0.0452</v>
       </c>
       <c r="U20" t="n">
-        <v>0.415</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>0.1061</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.6084</v>
+        <v>3.1109</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9497</v>
+        <v>-0.414</v>
       </c>
       <c r="F21" t="n">
-        <v>3.5582</v>
+        <v>3.5249</v>
       </c>
       <c r="G21" t="n">
         <v>0.6883</v>
@@ -2092,13 +2092,13 @@
         <v>2.2893</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.518</v>
+        <v>-0.0155</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9134</v>
+        <v>-0.3776</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3954</v>
+        <v>0.3621</v>
       </c>
       <c r="V21" t="n">
         <v>1.3975</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.8174</v>
+        <v>0.2355</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0373</v>
+        <v>-1.57</v>
       </c>
       <c r="F22" t="n">
-        <v>1.78</v>
+        <v>1.8055</v>
       </c>
       <c r="G22" t="n">
         <v>0.0722</v>
@@ -2170,13 +2170,13 @@
         <v>1.4568</v>
       </c>
       <c r="S22" t="n">
-        <v>2.1177</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>2.0093</v>
+        <v>0.402</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1084</v>
+        <v>0.1338</v>
       </c>
       <c r="V22" t="n">
         <v>0.4599</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0414</v>
+        <v>-0.3334</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7229</v>
+        <v>-4.1871</v>
       </c>
       <c r="F23" t="n">
-        <v>3.6816</v>
+        <v>3.8538</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5575</v>
@@ -2248,13 +2248,13 @@
         <v>2.9137</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0458</v>
+        <v>-0.3378</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1744</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1286</v>
+        <v>0.3008</v>
       </c>
       <c r="V23" t="n">
         <v>0.9376</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2065</v>
+        <v>-1.8835</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.0124</v>
+        <v>-4.1551</v>
       </c>
       <c r="F24" t="n">
-        <v>1.8058</v>
+        <v>2.2716</v>
       </c>
       <c r="G24" t="n">
         <v>1.2925</v>
@@ -2326,13 +2326,13 @@
         <v>1.4568</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1234</v>
+        <v>0.1997</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9786</v>
+        <v>-0.1214</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1448</v>
+        <v>0.3211</v>
       </c>
       <c r="V24" t="n">
         <v>-2.3351</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>31.7285</v>
+        <v>33.1572</v>
       </c>
       <c r="E25" t="n">
         <v>1.6853</v>
       </c>
       <c r="F25" t="n">
-        <v>30.0432</v>
+        <v>31.472</v>
       </c>
       <c r="G25" t="n">
         <v>19.8402</v>
@@ -2404,13 +2404,13 @@
         <v>19.7711</v>
       </c>
       <c r="S25" t="n">
-        <v>3.3241</v>
+        <v>4.7529</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8052</v>
+        <v>0.8053</v>
       </c>
       <c r="U25" t="n">
-        <v>2.5189</v>
+        <v>3.9477</v>
       </c>
       <c r="V25" t="n">
         <v>3.3609</v>
